--- a/data/trans_bre/P16A11-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,78</t>
+          <t>-1,2; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 9,65</t>
+          <t>0,82; 9,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 8,43</t>
+          <t>0,25; 8,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,09</t>
+          <t>-1,55; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 46,83</t>
+          <t>-7,92; 47,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 56,99</t>
+          <t>3,56; 57,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 63,1</t>
+          <t>0,55; 64,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 32,48</t>
+          <t>-6,78; 31,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,36</t>
+          <t>2,07; 8,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,22</t>
+          <t>0,13; 7,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 5,85</t>
+          <t>-0,96; 5,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,71</t>
+          <t>0,88; 12,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,79; 75,61</t>
+          <t>14,6; 79,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 54,04</t>
+          <t>0,97; 53,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 44,43</t>
+          <t>-7,2; 44,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 160,84</t>
+          <t>4,94; 163,62</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 7,74</t>
+          <t>0,41; 7,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,67</t>
+          <t>-1,33; 6,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 8,27</t>
+          <t>0,33; 8,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 47,76</t>
+          <t>-4,54; 50,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 71,1</t>
+          <t>2,34; 71,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 51,7</t>
+          <t>-8,61; 48,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 65,2</t>
+          <t>1,7; 63,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 276,28</t>
+          <t>-23,02; 270,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,06</t>
+          <t>1,3; 7,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,1</t>
+          <t>1,39; 8,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,42</t>
+          <t>-2,01; 5,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 5,63</t>
+          <t>-2,57; 6,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 69,38</t>
+          <t>10,47; 73,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 56,13</t>
+          <t>6,43; 53,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 39,94</t>
+          <t>-12,34; 35,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 29,51</t>
+          <t>-11,0; 32,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,65</t>
+          <t>2,25; 5,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,22</t>
+          <t>2,19; 6,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,68</t>
+          <t>1,14; 4,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 23,27</t>
+          <t>1,21; 21,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 47,7</t>
+          <t>16,41; 48,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 39,26</t>
+          <t>11,94; 38,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 33,25</t>
+          <t>7,41; 33,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 150,83</t>
+          <t>6,66; 131,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A11-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A11-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,02</t>
+          <t>-1,6; 6,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 9,52</t>
+          <t>0,81; 9,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,57</t>
+          <t>0,16; 8,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,92</t>
+          <t>-1,54; 5,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 47,0</t>
+          <t>-10,1; 47,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 57,71</t>
+          <t>3,82; 58,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 64,13</t>
+          <t>0,79; 65,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 31,89</t>
+          <t>-6,74; 30,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,54</t>
+          <t>1,82; 8,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 7,0</t>
+          <t>0,4; 7,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,7</t>
+          <t>-0,92; 5,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 12,78</t>
+          <t>-0,86; 4,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 79,26</t>
+          <t>12,99; 74,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 53,88</t>
+          <t>2,34; 52,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 44,1</t>
+          <t>-5,8; 42,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 163,62</t>
+          <t>-4,7; 33,36</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,05</t>
+          <t>-2,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>-12,7%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 7,81</t>
+          <t>0,18; 7,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,55</t>
+          <t>-1,0; 6,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 8,04</t>
+          <t>-0,11; 8,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 50,48</t>
+          <t>-6,02; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 71,72</t>
+          <t>0,74; 70,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 48,67</t>
+          <t>-6,05; 53,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 63,78</t>
+          <t>-0,64; 66,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 270,98</t>
+          <t>-27,93; 6,19</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,38</t>
+          <t>0,82; 7,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,66</t>
+          <t>1,0; 8,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,01</t>
+          <t>-1,48; 5,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 6,06</t>
+          <t>1,16; 7,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 73,16</t>
+          <t>5,8; 70,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 53,25</t>
+          <t>4,56; 51,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 35,77</t>
+          <t>-9,0; 37,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 32,48</t>
+          <t>5,52; 41,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,83</t>
+          <t>2,31; 5,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,17</t>
+          <t>2,18; 6,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,7</t>
+          <t>1,03; 4,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 21,93</t>
+          <t>0,1; 3,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,41; 48,5</t>
+          <t>17,09; 48,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,94; 38,67</t>
+          <t>12,42; 39,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 33,89</t>
+          <t>6,48; 34,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 131,33</t>
+          <t>0,52; 19,23</t>
         </is>
       </c>
     </row>
